--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260914.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>16,261,073</t>
+          <t>15,090,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>15,090,000</t>
+          <t>56,880,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>56,880,000</t>
+          <t>16,261,073</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>21,871,000</t>
+          <t>16,660,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>16,660,000</t>
+          <t>21,871,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>2,960,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2,960,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
